--- a/artfynd/A 33069-2025 artfynd.xlsx
+++ b/artfynd/A 33069-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115469249</v>
+        <v>120520547</v>
       </c>
       <c r="B2" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Väster om Velanda, Nrk</t>
+          <t>Velanda, Velanda, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>502955</v>
+        <v>503379</v>
       </c>
       <c r="R2" t="n">
-        <v>6561058</v>
+        <v>6561173</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,12 +745,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-10-27</t>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-10-27</t>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Hack o död gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -761,31 +776,51 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Britta Lidberg</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Britta Lidberg</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115469254</v>
+        <v>115469304</v>
       </c>
       <c r="B3" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57947</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,37 +828,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>102977</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Väster om Velanda, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503368</v>
+        <v>502992</v>
       </c>
       <c r="R3" t="n">
-        <v>6561422</v>
+        <v>6561059</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -853,6 +893,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-10-27</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Flög bland tallarna.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,15 +924,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115469255</v>
+        <v>118355045</v>
       </c>
       <c r="B4" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58826</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,37 +935,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>208242</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>eDNA</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Väster om Velanda, Nrk</t>
+          <t>Velanda, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503378</v>
+        <v>503068</v>
       </c>
       <c r="R4" t="n">
-        <v>6561419</v>
+        <v>6561292</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -949,12 +994,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-10-27</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-10-27</t>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>I samband med groddjursinventering vid projektering Velanda solpark. eDNA: 2 av 3 replikat positiva</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,27 +1019,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Britta Lidberg</t>
+          <t>Jonas Örnborg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Britta Lidberg</t>
+          <t>Jonas Örnborg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115469251</v>
+        <v>118355223</v>
       </c>
       <c r="B5" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58790</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,37 +1042,56 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>208245</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>lampa</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Väster om Velanda, Nrk</t>
+          <t>Velanda, Nrk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>502988</v>
+        <v>503086</v>
       </c>
       <c r="R5" t="n">
-        <v>6561141</v>
+        <v>6561301</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,12 +1115,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-10-27</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-10-27</t>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>I samband med groddjursinventering vid projektering Velanda solpark</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,27 +1140,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Britta Lidberg</t>
+          <t>Jonas Örnborg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Britta Lidberg</t>
+          <t>Jonas Örnborg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115469304</v>
+        <v>118355231</v>
       </c>
       <c r="B6" t="n">
-        <v>57284</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58817</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,16 +1163,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102977</v>
+        <v>208249</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1117,24 +1181,24 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>eDNA</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Väster om Velanda, Nrk</t>
+          <t>Velanda, Nrk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502992</v>
+        <v>503072</v>
       </c>
       <c r="R6" t="n">
-        <v>6561059</v>
+        <v>6561292</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1158,17 +1222,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-10-27</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-10-27</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Flög bland tallarna.</t>
+          <t>I samband med groddjursinventering vid projektering Velanda solpark. eDNA: 3 av 3 replikat positiva</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1183,27 +1247,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Britta Lidberg</t>
+          <t>Jonas Örnborg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Britta Lidberg</t>
+          <t>Jonas Örnborg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118355231</v>
+        <v>115469249</v>
       </c>
       <c r="B7" t="n">
-        <v>58133</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1211,42 +1270,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>208249</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>eDNA</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Velanda, Nrk</t>
+          <t>Väster om Velanda, Nrk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503072</v>
+        <v>502955</v>
       </c>
       <c r="R7" t="n">
-        <v>6561292</v>
+        <v>6561058</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1270,17 +1324,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2023-10-27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>I samband med groddjursinventering vid projektering Velanda solpark. eDNA: 3 av 3 replikat positiva</t>
+          <t>2023-10-27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1295,27 +1344,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jonas Örnborg</t>
+          <t>Britta Lidberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jonas Örnborg</t>
+          <t>Britta Lidberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118355045</v>
+        <v>115469251</v>
       </c>
       <c r="B8" t="n">
-        <v>58141</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1323,42 +1367,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>208242</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>eDNA</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Velanda, Nrk</t>
+          <t>Väster om Velanda, Nrk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>503068</v>
+        <v>502988</v>
       </c>
       <c r="R8" t="n">
-        <v>6561292</v>
+        <v>6561141</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1382,17 +1421,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2023-10-27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>I samband med groddjursinventering vid projektering Velanda solpark. eDNA: 2 av 3 replikat positiva</t>
+          <t>2023-10-27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1407,15 +1441,306 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jonas Örnborg</t>
+          <t>Britta Lidberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jonas Örnborg</t>
+          <t>Britta Lidberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>115469253</v>
+      </c>
+      <c r="B9" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Väster om Velanda, Nrk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>503088</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6561056</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Täby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-10-27</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-10-27</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Britta Lidberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Britta Lidberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>115469254</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Väster om Velanda, Nrk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>503368</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6561422</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Täby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-10-27</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-10-27</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Britta Lidberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Britta Lidberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>115469255</v>
+      </c>
+      <c r="B11" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Väster om Velanda, Nrk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>503378</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6561419</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Täby</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-10-27</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-10-27</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Britta Lidberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Britta Lidberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33069-2025 artfynd.xlsx
+++ b/artfynd/A 33069-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -814,6 +819,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120520547</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -921,6 +931,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115469304</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1028,6 +1043,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118355045</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1149,6 +1169,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118355223</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1256,6 +1281,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118355231</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1353,6 +1383,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115469249</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1450,6 +1485,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115469251</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1547,6 +1587,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115469253</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1644,6 +1689,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115469254</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1741,8 +1791,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115469255</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>